--- a/temp_doc/DATA KELAS FIX.xlsx
+++ b/temp_doc/DATA KELAS FIX.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Applications/XAMPP/xamppfiles/htdocs/cbt2.6admin/temp_doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE41044-C6F4-7D4D-AB6F-1E9945E0143E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F746C84F-26F2-BF4C-9159-6F7F1FACFE8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{AB72E732-1B4D-0449-8A67-D584FA100D85}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16160" xr2:uid="{AB72E732-1B4D-0449-8A67-D584FA100D85}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$29</definedName>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="47">
   <si>
     <t>id</t>
   </si>
@@ -65,117 +64,9 @@
     <t>TJKT</t>
   </si>
   <si>
-    <t>XII AKL 1</t>
-  </si>
-  <si>
-    <t>XII AKL 2</t>
-  </si>
-  <si>
-    <t>XII MPLB 1</t>
-  </si>
-  <si>
-    <t>XII MPLB 2</t>
-  </si>
-  <si>
-    <t>XII TJKT 1</t>
-  </si>
-  <si>
-    <t>XII TJKT 2</t>
-  </si>
-  <si>
-    <t>XII TJKT 3</t>
-  </si>
-  <si>
-    <t>XII DKV</t>
-  </si>
-  <si>
     <t>slug</t>
   </si>
   <si>
-    <t>XAKL2</t>
-  </si>
-  <si>
-    <t>XPM</t>
-  </si>
-  <si>
-    <t>XMPLB1</t>
-  </si>
-  <si>
-    <t>XMPLB2</t>
-  </si>
-  <si>
-    <t>XTJKT1</t>
-  </si>
-  <si>
-    <t>XTJKT2</t>
-  </si>
-  <si>
-    <t>XTJKT3</t>
-  </si>
-  <si>
-    <t>XTJKT4</t>
-  </si>
-  <si>
-    <t>XDKV</t>
-  </si>
-  <si>
-    <t>XIAKL1</t>
-  </si>
-  <si>
-    <t>XIAKL2</t>
-  </si>
-  <si>
-    <t>XIPM</t>
-  </si>
-  <si>
-    <t>XIMPLB1</t>
-  </si>
-  <si>
-    <t>XIMPLB2</t>
-  </si>
-  <si>
-    <t>XITJKT1</t>
-  </si>
-  <si>
-    <t>XITJKT2</t>
-  </si>
-  <si>
-    <t>XITJKT3</t>
-  </si>
-  <si>
-    <t>XIDKV</t>
-  </si>
-  <si>
-    <t>XIIAKL1</t>
-  </si>
-  <si>
-    <t>XIIAKL2</t>
-  </si>
-  <si>
-    <t>XIIPM</t>
-  </si>
-  <si>
-    <t>XIIMPLB1</t>
-  </si>
-  <si>
-    <t>XIIMPLB2</t>
-  </si>
-  <si>
-    <t>XIITJKT1</t>
-  </si>
-  <si>
-    <t>XIITJKT2</t>
-  </si>
-  <si>
-    <t>XIITJKT3</t>
-  </si>
-  <si>
-    <t>XIIDKV</t>
-  </si>
-  <si>
-    <t>XAKL1</t>
-  </si>
-  <si>
     <t>X AKL 1</t>
   </si>
   <si>
@@ -233,98 +124,68 @@
     <t>XI DKV</t>
   </si>
   <si>
-    <t>XII PM</t>
-  </si>
-  <si>
-    <t>X AKL 1_STS_2526</t>
-  </si>
-  <si>
-    <t>X AKL 2_STS_2526</t>
-  </si>
-  <si>
-    <t>X PM_STS_2526</t>
-  </si>
-  <si>
-    <t>X MPLB 1_STS_2526</t>
-  </si>
-  <si>
-    <t>X MPLB 2_STS_2526</t>
-  </si>
-  <si>
-    <t>X TJKT 1_STS_2526</t>
-  </si>
-  <si>
-    <t>X TJKT 2_STS_2526</t>
-  </si>
-  <si>
-    <t>X TJKT 3_STS_2526</t>
-  </si>
-  <si>
-    <t>X TJKT 4_STS_2526</t>
-  </si>
-  <si>
-    <t>X DKV_STS_2526</t>
-  </si>
-  <si>
-    <t>XI AKL 1_STS_2526</t>
-  </si>
-  <si>
-    <t>XI AKL 2_STS_2526</t>
-  </si>
-  <si>
-    <t>XI PM_STS_2526</t>
-  </si>
-  <si>
-    <t>XI MPLB 1_STS_2526</t>
-  </si>
-  <si>
-    <t>XI MPLB 2_STS_2526</t>
-  </si>
-  <si>
-    <t>XI TJKT 1_STS_2526</t>
-  </si>
-  <si>
-    <t>XI TJKT 2_STS_2526</t>
-  </si>
-  <si>
-    <t>XI TJKT 3_STS_2526</t>
-  </si>
-  <si>
-    <t>XI DKV_STS_2526</t>
-  </si>
-  <si>
-    <t>XII AKL 1_SAS_2526</t>
-  </si>
-  <si>
-    <t>XII AKL 2_SAS_2526</t>
-  </si>
-  <si>
-    <t>XII PM_SAS_2526</t>
-  </si>
-  <si>
-    <t>XII MPLB 1_SAS_2526</t>
-  </si>
-  <si>
-    <t>XII MPLB 2_SAS_2526</t>
-  </si>
-  <si>
-    <t>XII TJKT 1_SAS_2526</t>
-  </si>
-  <si>
-    <t>XII TJKT 2_SAS_2526</t>
-  </si>
-  <si>
-    <t>XII TJKT 3_SAS_2526</t>
-  </si>
-  <si>
-    <t>XII DKV_SAS_2526</t>
+    <t>X AKL 1_SAS_2526</t>
+  </si>
+  <si>
+    <t>X AKL 2_SAS_2526</t>
+  </si>
+  <si>
+    <t>X PM_SAS_2526</t>
+  </si>
+  <si>
+    <t>X MPLB 1_SAS_2526</t>
+  </si>
+  <si>
+    <t>X MPLB 2_SAS_2526</t>
+  </si>
+  <si>
+    <t>X TJKT 1_SAS_2526</t>
+  </si>
+  <si>
+    <t>X TJKT 2_SAS_2526</t>
+  </si>
+  <si>
+    <t>X TJKT 3_SAS_2526</t>
+  </si>
+  <si>
+    <t>X TJKT 4_SAS_2526</t>
+  </si>
+  <si>
+    <t>X DKV_SAS_2526</t>
+  </si>
+  <si>
+    <t>XI AKL 1_SAS_2526</t>
+  </si>
+  <si>
+    <t>XI AKL 2_SAS_2526</t>
+  </si>
+  <si>
+    <t>XI PM_SAS_2526</t>
+  </si>
+  <si>
+    <t>XI MPLB 1_SAS_2526</t>
+  </si>
+  <si>
+    <t>XI MPLB 2_SAS_2526</t>
+  </si>
+  <si>
+    <t>XI TJKT 1_SAS_2526</t>
+  </si>
+  <si>
+    <t>XI TJKT 2_SAS_2526</t>
+  </si>
+  <si>
+    <t>XI TJKT 3_SAS_2526</t>
+  </si>
+  <si>
+    <t>XI DKV_SAS_2526</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -337,13 +198,6 @@
       <sz val="14"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -373,11 +227,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -709,7 +562,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -719,11 +572,11 @@
       <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>45</v>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -733,11 +586,11 @@
       <c r="B3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>46</v>
+      <c r="C3" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -747,11 +600,11 @@
       <c r="B4" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>47</v>
+      <c r="C4" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -761,11 +614,11 @@
       <c r="B5" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>48</v>
+      <c r="C5" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -775,11 +628,11 @@
       <c r="B6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>49</v>
+      <c r="C6" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -789,11 +642,11 @@
       <c r="B7" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>50</v>
+      <c r="C7" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -803,11 +656,11 @@
       <c r="B8" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>51</v>
+      <c r="C8" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -817,11 +670,11 @@
       <c r="B9" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>52</v>
+      <c r="C9" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -831,11 +684,11 @@
       <c r="B10" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>53</v>
+      <c r="C10" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -845,11 +698,11 @@
       <c r="B11" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>54</v>
+      <c r="C11" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -859,11 +712,11 @@
       <c r="B12" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>55</v>
+      <c r="C12" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -873,11 +726,11 @@
       <c r="B13" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>56</v>
+      <c r="C13" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -887,11 +740,11 @@
       <c r="B14" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>57</v>
+      <c r="C14" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -901,11 +754,11 @@
       <c r="B15" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>58</v>
+      <c r="C15" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -915,11 +768,11 @@
       <c r="B16" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>59</v>
+      <c r="C16" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="D16" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -929,11 +782,11 @@
       <c r="B17" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>60</v>
+      <c r="C17" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="D17" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -943,11 +796,11 @@
       <c r="B18" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>61</v>
+      <c r="C18" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -957,11 +810,11 @@
       <c r="B19" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>62</v>
+      <c r="C19" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="D19" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -971,406 +824,42 @@
       <c r="B20" t="s">
         <v>4</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>63</v>
+      <c r="C20" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="D20" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>1020</v>
-      </c>
-      <c r="B21" t="s">
-        <v>3</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" t="s">
-        <v>84</v>
-      </c>
+      <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>1021</v>
-      </c>
-      <c r="B22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" t="s">
-        <v>85</v>
-      </c>
+      <c r="C22" s="2"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>1022</v>
-      </c>
-      <c r="B23" t="s">
-        <v>5</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D23" t="s">
-        <v>86</v>
-      </c>
+      <c r="C23" s="2"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>1023</v>
-      </c>
-      <c r="B24" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" t="s">
-        <v>87</v>
-      </c>
+      <c r="C24" s="2"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>1024</v>
-      </c>
-      <c r="B25" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" t="s">
-        <v>88</v>
-      </c>
+      <c r="C25" s="2"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>1025</v>
-      </c>
-      <c r="B26" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D26" t="s">
-        <v>89</v>
-      </c>
+      <c r="C26" s="2"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>1026</v>
-      </c>
-      <c r="B27" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D27" t="s">
-        <v>90</v>
-      </c>
+      <c r="C27" s="2"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>1027</v>
-      </c>
-      <c r="B28" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D28" t="s">
-        <v>91</v>
-      </c>
+      <c r="C28" s="2"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>1028</v>
-      </c>
-      <c r="B29" t="s">
-        <v>4</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" t="s">
-        <v>92</v>
-      </c>
+      <c r="C29" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7B619F6-725B-5A47-866E-C5048BC3F4F7}">
-  <dimension ref="A1:B28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="14.83203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" t="str">
-        <f>CONCATENATE(LOWER(A1),"_",2526)</f>
-        <v>xakl1_2526</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" t="str">
-        <f t="shared" ref="B2:B28" si="0">CONCATENATE(LOWER(A2),"_",2526)</f>
-        <v>xakl2_2526</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" t="str">
-        <f t="shared" si="0"/>
-        <v>xpm_2526</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" t="str">
-        <f t="shared" si="0"/>
-        <v>xmplb1_2526</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="str">
-        <f t="shared" si="0"/>
-        <v>xmplb2_2526</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" t="str">
-        <f t="shared" si="0"/>
-        <v>xtjkt1_2526</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" t="str">
-        <f t="shared" si="0"/>
-        <v>xtjkt2_2526</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" t="str">
-        <f t="shared" si="0"/>
-        <v>xtjkt3_2526</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" t="str">
-        <f t="shared" si="0"/>
-        <v>xtjkt4_2526</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" t="str">
-        <f t="shared" si="0"/>
-        <v>xdkv_2526</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" t="str">
-        <f t="shared" si="0"/>
-        <v>xiakl1_2526</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" t="str">
-        <f t="shared" si="0"/>
-        <v>xiakl2_2526</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" t="str">
-        <f t="shared" si="0"/>
-        <v>xipm_2526</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" t="str">
-        <f t="shared" si="0"/>
-        <v>ximplb1_2526</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" t="str">
-        <f t="shared" si="0"/>
-        <v>ximplb2_2526</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" t="str">
-        <f t="shared" si="0"/>
-        <v>xitjkt1_2526</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" t="str">
-        <f t="shared" si="0"/>
-        <v>xitjkt2_2526</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" t="str">
-        <f t="shared" si="0"/>
-        <v>xitjkt3_2526</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" t="str">
-        <f t="shared" si="0"/>
-        <v>xidkv_2526</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" t="str">
-        <f t="shared" si="0"/>
-        <v>xiiakl1_2526</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" t="str">
-        <f t="shared" si="0"/>
-        <v>xiiakl2_2526</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" t="str">
-        <f t="shared" si="0"/>
-        <v>xiipm_2526</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" t="str">
-        <f t="shared" si="0"/>
-        <v>xiimplb1_2526</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" t="str">
-        <f t="shared" si="0"/>
-        <v>xiimplb2_2526</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" t="str">
-        <f t="shared" si="0"/>
-        <v>xiitjkt1_2526</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" t="str">
-        <f t="shared" si="0"/>
-        <v>xiitjkt2_2526</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27" t="str">
-        <f t="shared" si="0"/>
-        <v>xiitjkt3_2526</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28" t="str">
-        <f t="shared" si="0"/>
-        <v>xiidkv_2526</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/temp_doc/DATA KELAS FIX.xlsx
+++ b/temp_doc/DATA KELAS FIX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Applications/XAMPP/xamppfiles/htdocs/cbt2.6admin/temp_doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F746C84F-26F2-BF4C-9159-6F7F1FACFE8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080F5791-6135-5341-A970-38517AA7592F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16160" xr2:uid="{AB72E732-1B4D-0449-8A67-D584FA100D85}"/>
+    <workbookView xWindow="4180" yWindow="600" windowWidth="28800" windowHeight="16160" xr2:uid="{AB72E732-1B4D-0449-8A67-D584FA100D85}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -124,61 +124,61 @@
     <t>XI DKV</t>
   </si>
   <si>
-    <t>X AKL 1_SAS_2526</t>
-  </si>
-  <si>
-    <t>X AKL 2_SAS_2526</t>
-  </si>
-  <si>
-    <t>X PM_SAS_2526</t>
-  </si>
-  <si>
-    <t>X MPLB 1_SAS_2526</t>
-  </si>
-  <si>
-    <t>X MPLB 2_SAS_2526</t>
-  </si>
-  <si>
-    <t>X TJKT 1_SAS_2526</t>
-  </si>
-  <si>
-    <t>X TJKT 2_SAS_2526</t>
-  </si>
-  <si>
-    <t>X TJKT 3_SAS_2526</t>
-  </si>
-  <si>
-    <t>X TJKT 4_SAS_2526</t>
-  </si>
-  <si>
-    <t>X DKV_SAS_2526</t>
-  </si>
-  <si>
-    <t>XI AKL 1_SAS_2526</t>
-  </si>
-  <si>
-    <t>XI AKL 2_SAS_2526</t>
-  </si>
-  <si>
-    <t>XI PM_SAS_2526</t>
-  </si>
-  <si>
-    <t>XI MPLB 1_SAS_2526</t>
-  </si>
-  <si>
-    <t>XI MPLB 2_SAS_2526</t>
-  </si>
-  <si>
-    <t>XI TJKT 1_SAS_2526</t>
-  </si>
-  <si>
-    <t>XI TJKT 2_SAS_2526</t>
-  </si>
-  <si>
-    <t>XI TJKT 3_SAS_2526</t>
-  </si>
-  <si>
-    <t>XI DKV_SAS_2526</t>
+    <t>X AKL 1_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>X AKL 2_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>X PM_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>X MPLB 1_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>X MPLB 2_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>X TJKT 1_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>X TJKT 2_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>X TJKT 3_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>X TJKT 4_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>X DKV_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>XI AKL 1_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>XI AKL 2_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>XI PM_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>XI MPLB 1_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>XI MPLB 2_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>XI TJKT 1_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>XI TJKT 2_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>XI TJKT 3_ULANGAN HARIAN_2526</t>
+  </si>
+  <si>
+    <t>XI DKV_ULANGAN HARIAN_2526</t>
   </si>
 </sst>
 </file>
@@ -548,7 +548,7 @@
   <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.2">

--- a/temp_doc/DATA KELAS FIX.xlsx
+++ b/temp_doc/DATA KELAS FIX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Applications/XAMPP/xamppfiles/htdocs/cbt2.6admin/temp_doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080F5791-6135-5341-A970-38517AA7592F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29262670-4D82-084E-9C5E-86F04EB07594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4180" yWindow="600" windowWidth="28800" windowHeight="16160" xr2:uid="{AB72E732-1B4D-0449-8A67-D584FA100D85}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16100" xr2:uid="{AB72E732-1B4D-0449-8A67-D584FA100D85}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -124,61 +124,61 @@
     <t>XI DKV</t>
   </si>
   <si>
-    <t>X AKL 1_ULANGAN HARIAN_2526</t>
-  </si>
-  <si>
-    <t>X AKL 2_ULANGAN HARIAN_2526</t>
-  </si>
-  <si>
-    <t>X PM_ULANGAN HARIAN_2526</t>
-  </si>
-  <si>
-    <t>X MPLB 1_ULANGAN HARIAN_2526</t>
-  </si>
-  <si>
-    <t>X MPLB 2_ULANGAN HARIAN_2526</t>
-  </si>
-  <si>
-    <t>X TJKT 1_ULANGAN HARIAN_2526</t>
-  </si>
-  <si>
-    <t>X TJKT 2_ULANGAN HARIAN_2526</t>
-  </si>
-  <si>
-    <t>X TJKT 3_ULANGAN HARIAN_2526</t>
-  </si>
-  <si>
-    <t>X TJKT 4_ULANGAN HARIAN_2526</t>
-  </si>
-  <si>
-    <t>X DKV_ULANGAN HARIAN_2526</t>
-  </si>
-  <si>
-    <t>XI AKL 1_ULANGAN HARIAN_2526</t>
-  </si>
-  <si>
-    <t>XI AKL 2_ULANGAN HARIAN_2526</t>
-  </si>
-  <si>
-    <t>XI PM_ULANGAN HARIAN_2526</t>
-  </si>
-  <si>
-    <t>XI MPLB 1_ULANGAN HARIAN_2526</t>
-  </si>
-  <si>
-    <t>XI MPLB 2_ULANGAN HARIAN_2526</t>
-  </si>
-  <si>
-    <t>XI TJKT 1_ULANGAN HARIAN_2526</t>
-  </si>
-  <si>
-    <t>XI TJKT 2_ULANGAN HARIAN_2526</t>
-  </si>
-  <si>
-    <t>XI TJKT 3_ULANGAN HARIAN_2526</t>
-  </si>
-  <si>
-    <t>XI DKV_ULANGAN HARIAN_2526</t>
+    <t>X AKL 1_SAS_2025/2026</t>
+  </si>
+  <si>
+    <t>X AKL 2_SAS_2025/2026</t>
+  </si>
+  <si>
+    <t>X PM_SAS_2025/2026</t>
+  </si>
+  <si>
+    <t>X MPLB 1_SAS_2025/2026</t>
+  </si>
+  <si>
+    <t>X MPLB 2_SAS_2025/2026</t>
+  </si>
+  <si>
+    <t>X TJKT 1_SAS_2025/2026</t>
+  </si>
+  <si>
+    <t>X TJKT 2_SAS_2025/2026</t>
+  </si>
+  <si>
+    <t>X TJKT 3_SAS_2025/2026</t>
+  </si>
+  <si>
+    <t>X TJKT 4_SAS_2025/2026</t>
+  </si>
+  <si>
+    <t>X DKV_SAS_2025/2026</t>
+  </si>
+  <si>
+    <t>XI AKL 1_SAS_2025/2026</t>
+  </si>
+  <si>
+    <t>XI AKL 2_SAS_2025/2026</t>
+  </si>
+  <si>
+    <t>XI PM_SAS_2025/2026</t>
+  </si>
+  <si>
+    <t>XI MPLB 1_SAS_2025/2026</t>
+  </si>
+  <si>
+    <t>XI MPLB 2_SAS_2025/2026</t>
+  </si>
+  <si>
+    <t>XI TJKT 1_SAS_2025/2026</t>
+  </si>
+  <si>
+    <t>XI TJKT 2_SAS_2025/2026</t>
+  </si>
+  <si>
+    <t>XI TJKT 3_SAS_2025/2026</t>
+  </si>
+  <si>
+    <t>XI DKV_SAS_2025/2026</t>
   </si>
 </sst>
 </file>

--- a/temp_doc/DATA KELAS FIX.xlsx
+++ b/temp_doc/DATA KELAS FIX.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Applications/XAMPP/xamppfiles/htdocs/cbt2.6admin/temp_doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29262670-4D82-084E-9C5E-86F04EB07594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40358B01-E0D1-F742-80E1-E96F55D0AA7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16100" xr2:uid="{AB72E732-1B4D-0449-8A67-D584FA100D85}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$29</definedName>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="39">
   <si>
     <t>id</t>
   </si>
@@ -124,61 +125,37 @@
     <t>XI DKV</t>
   </si>
   <si>
-    <t>X AKL 1_SAS_2025/2026</t>
-  </si>
-  <si>
-    <t>X AKL 2_SAS_2025/2026</t>
-  </si>
-  <si>
-    <t>X PM_SAS_2025/2026</t>
-  </si>
-  <si>
-    <t>X MPLB 1_SAS_2025/2026</t>
-  </si>
-  <si>
-    <t>X MPLB 2_SAS_2025/2026</t>
-  </si>
-  <si>
-    <t>X TJKT 1_SAS_2025/2026</t>
-  </si>
-  <si>
-    <t>X TJKT 2_SAS_2025/2026</t>
-  </si>
-  <si>
-    <t>X TJKT 3_SAS_2025/2026</t>
-  </si>
-  <si>
-    <t>X TJKT 4_SAS_2025/2026</t>
-  </si>
-  <si>
-    <t>X DKV_SAS_2025/2026</t>
-  </si>
-  <si>
-    <t>XI AKL 1_SAS_2025/2026</t>
-  </si>
-  <si>
-    <t>XI AKL 2_SAS_2025/2026</t>
-  </si>
-  <si>
-    <t>XI PM_SAS_2025/2026</t>
-  </si>
-  <si>
-    <t>XI MPLB 1_SAS_2025/2026</t>
-  </si>
-  <si>
-    <t>XI MPLB 2_SAS_2025/2026</t>
-  </si>
-  <si>
-    <t>XI TJKT 1_SAS_2025/2026</t>
-  </si>
-  <si>
-    <t>XI TJKT 2_SAS_2025/2026</t>
-  </si>
-  <si>
-    <t>XI TJKT 3_SAS_2025/2026</t>
-  </si>
-  <si>
-    <t>XI DKV_SAS_2025/2026</t>
+    <t>XI TJKT 4</t>
+  </si>
+  <si>
+    <t>XII AKL 1</t>
+  </si>
+  <si>
+    <t>XII AKL 2</t>
+  </si>
+  <si>
+    <t>XII PM</t>
+  </si>
+  <si>
+    <t>XII MPLB 1</t>
+  </si>
+  <si>
+    <t>XII MPLB 2</t>
+  </si>
+  <si>
+    <t>XII TJKT 1</t>
+  </si>
+  <si>
+    <t>XII TJKT 2</t>
+  </si>
+  <si>
+    <t>XII TJKT 3</t>
+  </si>
+  <si>
+    <t>XII TJKT 4</t>
+  </si>
+  <si>
+    <t>XII DKV</t>
   </si>
 </sst>
 </file>
@@ -545,7 +522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{664577AF-41FC-0C49-BD7B-86162BAED619}">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="31.33203125" bestFit="1" customWidth="1"/>
@@ -575,8 +552,9 @@
       <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
-        <v>28</v>
+      <c r="D2" t="str">
+        <f>_xlfn.CONCAT(C2,"_","TRIAL","_","2026/2027")</f>
+        <v>X AKL 1_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -589,8 +567,9 @@
       <c r="C3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
-        <v>29</v>
+      <c r="D3" t="str">
+        <f t="shared" ref="D3:D30" si="0">_xlfn.CONCAT(C3,"_","TRIAL","_","2026/2027")</f>
+        <v>X AKL 2_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -603,8 +582,9 @@
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D4" t="s">
-        <v>30</v>
+      <c r="D4" t="str">
+        <f t="shared" si="0"/>
+        <v>X PM_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -617,8 +597,9 @@
       <c r="C5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D5" t="s">
-        <v>31</v>
+      <c r="D5" t="str">
+        <f t="shared" si="0"/>
+        <v>X MPLB 1_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -631,8 +612,9 @@
       <c r="C6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D6" t="s">
-        <v>32</v>
+      <c r="D6" t="str">
+        <f t="shared" si="0"/>
+        <v>X MPLB 2_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -645,8 +627,9 @@
       <c r="C7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D7" t="s">
-        <v>33</v>
+      <c r="D7" t="str">
+        <f t="shared" si="0"/>
+        <v>X TJKT 1_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -659,8 +642,9 @@
       <c r="C8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D8" t="s">
-        <v>34</v>
+      <c r="D8" t="str">
+        <f t="shared" si="0"/>
+        <v>X TJKT 2_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -673,8 +657,9 @@
       <c r="C9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D9" t="s">
-        <v>35</v>
+      <c r="D9" t="str">
+        <f t="shared" si="0"/>
+        <v>X TJKT 3_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -687,8 +672,9 @@
       <c r="C10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D10" t="s">
-        <v>36</v>
+      <c r="D10" t="str">
+        <f t="shared" si="0"/>
+        <v>X TJKT 4_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -701,8 +687,9 @@
       <c r="C11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D11" t="s">
-        <v>37</v>
+      <c r="D11" t="str">
+        <f t="shared" si="0"/>
+        <v>X DKV_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -715,8 +702,9 @@
       <c r="C12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D12" t="s">
-        <v>38</v>
+      <c r="D12" t="str">
+        <f t="shared" si="0"/>
+        <v>XI AKL 1_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -729,8 +717,9 @@
       <c r="C13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D13" t="s">
-        <v>39</v>
+      <c r="D13" t="str">
+        <f t="shared" si="0"/>
+        <v>XI AKL 2_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -743,8 +732,9 @@
       <c r="C14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D14" t="s">
-        <v>40</v>
+      <c r="D14" t="str">
+        <f t="shared" si="0"/>
+        <v>XI PM_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -757,8 +747,9 @@
       <c r="C15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D15" t="s">
-        <v>41</v>
+      <c r="D15" t="str">
+        <f t="shared" si="0"/>
+        <v>XI MPLB 1_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -771,8 +762,9 @@
       <c r="C16" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D16" t="s">
-        <v>42</v>
+      <c r="D16" t="str">
+        <f t="shared" si="0"/>
+        <v>XI MPLB 2_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -785,8 +777,9 @@
       <c r="C17" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D17" t="s">
-        <v>43</v>
+      <c r="D17" t="str">
+        <f t="shared" si="0"/>
+        <v>XI TJKT 1_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -799,8 +792,9 @@
       <c r="C18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D18" t="s">
-        <v>44</v>
+      <c r="D18" t="str">
+        <f t="shared" si="0"/>
+        <v>XI TJKT 2_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -813,8 +807,9 @@
       <c r="C19" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D19" t="s">
-        <v>45</v>
+      <c r="D19" t="str">
+        <f t="shared" si="0"/>
+        <v>XI TJKT 3_TRIAL_2026/2027</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -822,44 +817,228 @@
         <v>1019</v>
       </c>
       <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" t="str">
+        <f t="shared" si="0"/>
+        <v>XI TJKT 4_TRIAL_2026/2027</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>1020</v>
+      </c>
+      <c r="B21" t="s">
         <v>4</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D20" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C21" s="2"/>
+      <c r="D21" t="str">
+        <f t="shared" si="0"/>
+        <v>XI DKV_TRIAL_2026/2027</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C22" s="2"/>
+      <c r="A22">
+        <v>1021</v>
+      </c>
+      <c r="B22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" t="str">
+        <f t="shared" si="0"/>
+        <v>XII AKL 1_TRIAL_2026/2027</v>
+      </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C23" s="2"/>
+      <c r="A23">
+        <v>1022</v>
+      </c>
+      <c r="B23" t="s">
+        <v>3</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" t="str">
+        <f t="shared" si="0"/>
+        <v>XII AKL 2_TRIAL_2026/2027</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C24" s="2"/>
+      <c r="A24">
+        <v>1023</v>
+      </c>
+      <c r="B24" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" t="str">
+        <f t="shared" si="0"/>
+        <v>XII PM_TRIAL_2026/2027</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C25" s="2"/>
+      <c r="A25">
+        <v>1024</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" t="str">
+        <f t="shared" si="0"/>
+        <v>XII MPLB 1_TRIAL_2026/2027</v>
+      </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C26" s="2"/>
+      <c r="A26">
+        <v>1025</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" t="str">
+        <f t="shared" si="0"/>
+        <v>XII MPLB 2_TRIAL_2026/2027</v>
+      </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C27" s="2"/>
+      <c r="A27">
+        <v>1026</v>
+      </c>
+      <c r="B27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" t="str">
+        <f t="shared" si="0"/>
+        <v>XII TJKT 1_TRIAL_2026/2027</v>
+      </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C28" s="2"/>
+      <c r="A28">
+        <v>1027</v>
+      </c>
+      <c r="B28" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" t="str">
+        <f t="shared" si="0"/>
+        <v>XII TJKT 2_TRIAL_2026/2027</v>
+      </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C29" s="2"/>
+      <c r="A29">
+        <v>1028</v>
+      </c>
+      <c r="B29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D29" t="str">
+        <f t="shared" si="0"/>
+        <v>XII TJKT 3_TRIAL_2026/2027</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>1029</v>
+      </c>
+      <c r="B30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" t="str">
+        <f t="shared" si="0"/>
+        <v>XII DKV_TRIAL_2026/2027</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26B4ADE2-3FAD-DE4B-ADBE-3FD4743899CD}">
+  <dimension ref="A1:A10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/temp_doc/DATA KELAS FIX.xlsx
+++ b/temp_doc/DATA KELAS FIX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Applications/XAMPP/xamppfiles/htdocs/cbt2.6admin/temp_doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40358B01-E0D1-F742-80E1-E96F55D0AA7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD86858D-9CE7-5544-B475-A243E2DCFBBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16100" xr2:uid="{AB72E732-1B4D-0449-8A67-D584FA100D85}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15840" xr2:uid="{AB72E732-1B4D-0449-8A67-D584FA100D85}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -553,8 +553,8 @@
         <v>9</v>
       </c>
       <c r="D2" t="str">
-        <f>_xlfn.CONCAT(C2,"_","TRIAL","_","2026/2027")</f>
-        <v>X AKL 1_TRIAL_2026/2027</v>
+        <f>_xlfn.CONCAT(C2,"_","STS_GANJIL","_","2026/2027")</f>
+        <v>X AKL 1_STS_GANJIL_2026/2027</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -568,8 +568,8 @@
         <v>10</v>
       </c>
       <c r="D3" t="str">
-        <f t="shared" ref="D3:D30" si="0">_xlfn.CONCAT(C3,"_","TRIAL","_","2026/2027")</f>
-        <v>X AKL 2_TRIAL_2026/2027</v>
+        <f t="shared" ref="D3:D30" si="0">_xlfn.CONCAT(C3,"_","STS_GANJIL","_","2026/2027")</f>
+        <v>X AKL 2_STS_GANJIL_2026/2027</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -584,7 +584,7 @@
       </c>
       <c r="D4" t="str">
         <f t="shared" si="0"/>
-        <v>X PM_TRIAL_2026/2027</v>
+        <v>X PM_STS_GANJIL_2026/2027</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -599,7 +599,7 @@
       </c>
       <c r="D5" t="str">
         <f t="shared" si="0"/>
-        <v>X MPLB 1_TRIAL_2026/2027</v>
+        <v>X MPLB 1_STS_GANJIL_2026/2027</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -614,7 +614,7 @@
       </c>
       <c r="D6" t="str">
         <f t="shared" si="0"/>
-        <v>X MPLB 2_TRIAL_2026/2027</v>
+        <v>X MPLB 2_STS_GANJIL_2026/2027</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -629,7 +629,7 @@
       </c>
       <c r="D7" t="str">
         <f t="shared" si="0"/>
-        <v>X TJKT 1_TRIAL_2026/2027</v>
+        <v>X TJKT 1_STS_GANJIL_2026/2027</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -644,7 +644,7 @@
       </c>
       <c r="D8" t="str">
         <f t="shared" si="0"/>
-        <v>X TJKT 2_TRIAL_2026/2027</v>
+        <v>X TJKT 2_STS_GANJIL_2026/2027</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -659,7 +659,7 @@
       </c>
       <c r="D9" t="str">
         <f t="shared" si="0"/>
-        <v>X TJKT 3_TRIAL_2026/2027</v>
+        <v>X TJKT 3_STS_GANJIL_2026/2027</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -674,7 +674,7 @@
       </c>
       <c r="D10" t="str">
         <f t="shared" si="0"/>
-        <v>X TJKT 4_TRIAL_2026/2027</v>
+        <v>X TJKT 4_STS_GANJIL_2026/2027</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -689,7 +689,7 @@
       </c>
       <c r="D11" t="str">
         <f t="shared" si="0"/>
-        <v>X DKV_TRIAL_2026/2027</v>
+        <v>X DKV_STS_GANJIL_2026/2027</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -704,7 +704,7 @@
       </c>
       <c r="D12" t="str">
         <f t="shared" si="0"/>
-        <v>XI AKL 1_TRIAL_2026/2027</v>
+        <v>XI AKL 1_STS_GANJIL_2026/2027</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -719,7 +719,7 @@
       </c>
       <c r="D13" t="str">
         <f t="shared" si="0"/>
-        <v>XI AKL 2_TRIAL_2026/2027</v>
+        <v>XI AKL 2_STS_GANJIL_2026/2027</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -734,7 +734,7 @@
       </c>
       <c r="D14" t="str">
         <f t="shared" si="0"/>
-        <v>XI PM_TRIAL_2026/2027</v>
+        <v>XI PM_STS_GANJIL_2026/2027</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -749,7 +749,7 @@
       </c>
       <c r="D15" t="str">
         <f t="shared" si="0"/>
-        <v>XI MPLB 1_TRIAL_2026/2027</v>
+        <v>XI MPLB 1_STS_GANJIL_2026/2027</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -764,7 +764,7 @@
       </c>
       <c r="D16" t="str">
         <f t="shared" si="0"/>
-        <v>XI MPLB 2_TRIAL_2026/2027</v>
+        <v>XI MPLB 2_STS_GANJIL_2026/2027</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -779,7 +779,7 @@
       </c>
       <c r="D17" t="str">
         <f t="shared" si="0"/>
-        <v>XI TJKT 1_TRIAL_2026/2027</v>
+        <v>XI TJKT 1_STS_GANJIL_2026/2027</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -794,7 +794,7 @@
       </c>
       <c r="D18" t="str">
         <f t="shared" si="0"/>
-        <v>XI TJKT 2_TRIAL_2026/2027</v>
+        <v>XI TJKT 2_STS_GANJIL_2026/2027</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -809,7 +809,7 @@
       </c>
       <c r="D19" t="str">
         <f t="shared" si="0"/>
-        <v>XI TJKT 3_TRIAL_2026/2027</v>
+        <v>XI TJKT 3_STS_GANJIL_2026/2027</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -824,7 +824,7 @@
       </c>
       <c r="D20" t="str">
         <f t="shared" si="0"/>
-        <v>XI TJKT 4_TRIAL_2026/2027</v>
+        <v>XI TJKT 4_STS_GANJIL_2026/2027</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -839,7 +839,7 @@
       </c>
       <c r="D21" t="str">
         <f t="shared" si="0"/>
-        <v>XI DKV_TRIAL_2026/2027</v>
+        <v>XI DKV_STS_GANJIL_2026/2027</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
@@ -854,7 +854,7 @@
       </c>
       <c r="D22" t="str">
         <f t="shared" si="0"/>
-        <v>XII AKL 1_TRIAL_2026/2027</v>
+        <v>XII AKL 1_STS_GANJIL_2026/2027</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
@@ -869,7 +869,7 @@
       </c>
       <c r="D23" t="str">
         <f t="shared" si="0"/>
-        <v>XII AKL 2_TRIAL_2026/2027</v>
+        <v>XII AKL 2_STS_GANJIL_2026/2027</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
@@ -884,7 +884,7 @@
       </c>
       <c r="D24" t="str">
         <f t="shared" si="0"/>
-        <v>XII PM_TRIAL_2026/2027</v>
+        <v>XII PM_STS_GANJIL_2026/2027</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
@@ -899,7 +899,7 @@
       </c>
       <c r="D25" t="str">
         <f t="shared" si="0"/>
-        <v>XII MPLB 1_TRIAL_2026/2027</v>
+        <v>XII MPLB 1_STS_GANJIL_2026/2027</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
@@ -914,7 +914,7 @@
       </c>
       <c r="D26" t="str">
         <f t="shared" si="0"/>
-        <v>XII MPLB 2_TRIAL_2026/2027</v>
+        <v>XII MPLB 2_STS_GANJIL_2026/2027</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
@@ -929,7 +929,7 @@
       </c>
       <c r="D27" t="str">
         <f t="shared" si="0"/>
-        <v>XII TJKT 1_TRIAL_2026/2027</v>
+        <v>XII TJKT 1_STS_GANJIL_2026/2027</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
@@ -944,7 +944,7 @@
       </c>
       <c r="D28" t="str">
         <f t="shared" si="0"/>
-        <v>XII TJKT 2_TRIAL_2026/2027</v>
+        <v>XII TJKT 2_STS_GANJIL_2026/2027</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
@@ -959,7 +959,7 @@
       </c>
       <c r="D29" t="str">
         <f t="shared" si="0"/>
-        <v>XII TJKT 3_TRIAL_2026/2027</v>
+        <v>XII TJKT 3_STS_GANJIL_2026/2027</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
@@ -974,7 +974,7 @@
       </c>
       <c r="D30" t="str">
         <f t="shared" si="0"/>
-        <v>XII DKV_TRIAL_2026/2027</v>
+        <v>XII DKV_STS_GANJIL_2026/2027</v>
       </c>
     </row>
   </sheetData>
